--- a/E/SLK01D.xlsx
+++ b/E/SLK01D.xlsx
@@ -244,7 +244,7 @@
     <t>20106148</t>
   </si>
   <si>
-    <t>KR.TOAST SOES CHO 51</t>
+    <t>KR.TOAST SOES CHO 72</t>
   </si>
   <si>
     <t>20094497</t>
